--- a/diseases/d105/1995-1999.xlsx
+++ b/diseases/d105/1995-1999.xlsx
@@ -1803,7 +1803,7 @@
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN7" t="b">
@@ -2603,7 +2603,7 @@
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN11" t="b">
@@ -3403,7 +3403,7 @@
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN15" t="b">
@@ -4203,7 +4203,7 @@
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN19" t="b">
@@ -5003,7 +5003,7 @@
       </c>
       <c r="AM23" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN23" t="b">
@@ -5803,7 +5803,7 @@
       </c>
       <c r="AM27" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN27" t="b">
@@ -6603,7 +6603,7 @@
       </c>
       <c r="AM31" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN31" t="b">
@@ -7403,7 +7403,7 @@
       </c>
       <c r="AM35" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN35" t="b">
@@ -8203,7 +8203,7 @@
       </c>
       <c r="AM39" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN39" t="b">
@@ -9003,7 +9003,7 @@
       </c>
       <c r="AM43" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN43" t="b">
@@ -9803,7 +9803,7 @@
       </c>
       <c r="AM47" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN47" t="b">
@@ -10603,7 +10603,7 @@
       </c>
       <c r="AM51" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN51" t="b">
@@ -11793,7 +11793,7 @@
       </c>
       <c r="AM57" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN57" t="b">
@@ -12593,7 +12593,7 @@
       </c>
       <c r="AM61" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN61" t="b">
@@ -13393,7 +13393,7 @@
       </c>
       <c r="AM65" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN65" t="b">
@@ -14193,7 +14193,7 @@
       </c>
       <c r="AM69" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN69" t="b">
@@ -14993,7 +14993,7 @@
       </c>
       <c r="AM73" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN73" t="b">
@@ -15793,7 +15793,7 @@
       </c>
       <c r="AM77" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN77" t="b">
@@ -16593,7 +16593,7 @@
       </c>
       <c r="AM81" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN81" t="b">
@@ -17393,7 +17393,7 @@
       </c>
       <c r="AM85" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN85" t="b">
@@ -18193,7 +18193,7 @@
       </c>
       <c r="AM89" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN89" t="b">
@@ -18993,7 +18993,7 @@
       </c>
       <c r="AM93" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN93" t="b">
@@ -19793,7 +19793,7 @@
       </c>
       <c r="AM97" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN97" t="b">
@@ -20593,7 +20593,7 @@
       </c>
       <c r="AM101" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN101" t="b">
@@ -22167,7 +22167,7 @@
       </c>
       <c r="AM109" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN109" t="b">
@@ -23112,7 +23112,7 @@
       </c>
       <c r="AM114" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN114" t="b">
@@ -24057,7 +24057,7 @@
       </c>
       <c r="AM119" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN119" t="b">
@@ -25002,7 +25002,7 @@
       </c>
       <c r="AM124" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN124" t="b">
@@ -25947,7 +25947,7 @@
       </c>
       <c r="AM129" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN129" t="b">
@@ -26892,7 +26892,7 @@
       </c>
       <c r="AM134" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN134" t="b">
@@ -27837,7 +27837,7 @@
       </c>
       <c r="AM139" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN139" t="b">
@@ -28782,7 +28782,7 @@
       </c>
       <c r="AM144" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN144" t="b">
@@ -29727,7 +29727,7 @@
       </c>
       <c r="AM149" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN149" t="b">
@@ -30672,7 +30672,7 @@
       </c>
       <c r="AM154" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN154" t="b">
@@ -31617,7 +31617,7 @@
       </c>
       <c r="AM159" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN159" t="b">
@@ -32562,7 +32562,7 @@
       </c>
       <c r="AM164" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN164" t="b">
@@ -34136,7 +34136,7 @@
       </c>
       <c r="AM172" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN172" t="b">
@@ -35081,7 +35081,7 @@
       </c>
       <c r="AM177" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN177" t="b">
@@ -36026,7 +36026,7 @@
       </c>
       <c r="AM182" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN182" t="b">
@@ -36971,7 +36971,7 @@
       </c>
       <c r="AM187" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN187" t="b">
@@ -37916,7 +37916,7 @@
       </c>
       <c r="AM192" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN192" t="b">
@@ -38861,7 +38861,7 @@
       </c>
       <c r="AM197" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN197" t="b">
@@ -39806,7 +39806,7 @@
       </c>
       <c r="AM202" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN202" t="b">
@@ -40751,7 +40751,7 @@
       </c>
       <c r="AM207" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN207" t="b">
@@ -41696,7 +41696,7 @@
       </c>
       <c r="AM212" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN212" t="b">
@@ -42641,7 +42641,7 @@
       </c>
       <c r="AM217" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN217" t="b">
@@ -43586,7 +43586,7 @@
       </c>
       <c r="AM222" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN222" t="b">
@@ -44531,7 +44531,7 @@
       </c>
       <c r="AM227" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN227" t="b">
@@ -46105,7 +46105,7 @@
       </c>
       <c r="AM235" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN235" t="b">
@@ -47050,7 +47050,7 @@
       </c>
       <c r="AM240" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN240" t="b">
@@ -47995,7 +47995,7 @@
       </c>
       <c r="AM245" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN245" t="b">
@@ -48940,7 +48940,7 @@
       </c>
       <c r="AM250" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN250" t="b">
@@ -49885,7 +49885,7 @@
       </c>
       <c r="AM255" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN255" t="b">
@@ -50830,7 +50830,7 @@
       </c>
       <c r="AM260" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN260" t="b">
@@ -51775,7 +51775,7 @@
       </c>
       <c r="AM265" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN265" t="b">
@@ -52720,7 +52720,7 @@
       </c>
       <c r="AM270" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN270" t="b">
@@ -53665,7 +53665,7 @@
       </c>
       <c r="AM275" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN275" t="b">
@@ -54610,7 +54610,7 @@
       </c>
       <c r="AM280" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN280" t="b">
@@ -55555,7 +55555,7 @@
       </c>
       <c r="AM285" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN285" t="b">
@@ -56500,7 +56500,7 @@
       </c>
       <c r="AM290" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN290" t="b">

--- a/diseases/d105/1995-1999.xlsx
+++ b/diseases/d105/1995-1999.xlsx
@@ -1803,7 +1803,7 @@
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN7" t="b">
@@ -2603,7 +2603,7 @@
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN11" t="b">
@@ -3403,7 +3403,7 @@
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN15" t="b">
@@ -4203,7 +4203,7 @@
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN19" t="b">
@@ -5003,7 +5003,7 @@
       </c>
       <c r="AM23" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN23" t="b">
@@ -5803,7 +5803,7 @@
       </c>
       <c r="AM27" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN27" t="b">
@@ -6603,7 +6603,7 @@
       </c>
       <c r="AM31" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN31" t="b">
@@ -7403,7 +7403,7 @@
       </c>
       <c r="AM35" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN35" t="b">
@@ -8203,7 +8203,7 @@
       </c>
       <c r="AM39" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN39" t="b">
@@ -9003,7 +9003,7 @@
       </c>
       <c r="AM43" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN43" t="b">
@@ -9803,7 +9803,7 @@
       </c>
       <c r="AM47" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN47" t="b">
@@ -10603,7 +10603,7 @@
       </c>
       <c r="AM51" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN51" t="b">
@@ -11793,7 +11793,7 @@
       </c>
       <c r="AM57" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN57" t="b">
@@ -12593,7 +12593,7 @@
       </c>
       <c r="AM61" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN61" t="b">
@@ -13393,7 +13393,7 @@
       </c>
       <c r="AM65" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN65" t="b">
@@ -14193,7 +14193,7 @@
       </c>
       <c r="AM69" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN69" t="b">
@@ -14993,7 +14993,7 @@
       </c>
       <c r="AM73" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN73" t="b">
@@ -15793,7 +15793,7 @@
       </c>
       <c r="AM77" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN77" t="b">
@@ -16593,7 +16593,7 @@
       </c>
       <c r="AM81" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN81" t="b">
@@ -17393,7 +17393,7 @@
       </c>
       <c r="AM85" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN85" t="b">
@@ -18193,7 +18193,7 @@
       </c>
       <c r="AM89" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN89" t="b">
@@ -18993,7 +18993,7 @@
       </c>
       <c r="AM93" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN93" t="b">
@@ -19793,7 +19793,7 @@
       </c>
       <c r="AM97" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN97" t="b">
@@ -20593,7 +20593,7 @@
       </c>
       <c r="AM101" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN101" t="b">
@@ -21543,6 +21543,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA106" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO106" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -22167,7 +22172,7 @@
       </c>
       <c r="AM109" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN109" t="b">
@@ -22727,6 +22732,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA112" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO112" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -23112,7 +23122,7 @@
       </c>
       <c r="AM114" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN114" t="b">
@@ -23672,6 +23682,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA117" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO117" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -24057,7 +24072,7 @@
       </c>
       <c r="AM119" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN119" t="b">
@@ -24617,6 +24632,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA122" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO122" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -25002,7 +25022,7 @@
       </c>
       <c r="AM124" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN124" t="b">
@@ -25562,6 +25582,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA127" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO127" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -25947,7 +25972,7 @@
       </c>
       <c r="AM129" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN129" t="b">
@@ -26507,6 +26532,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA132" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO132" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -26892,7 +26922,7 @@
       </c>
       <c r="AM134" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN134" t="b">
@@ -27452,6 +27482,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA137" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO137" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -27837,7 +27872,7 @@
       </c>
       <c r="AM139" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN139" t="b">
@@ -28397,6 +28432,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA142" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO142" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -28782,7 +28822,7 @@
       </c>
       <c r="AM144" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN144" t="b">
@@ -29342,6 +29382,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA147" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO147" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -29727,7 +29772,7 @@
       </c>
       <c r="AM149" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN149" t="b">
@@ -30287,6 +30332,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA152" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO152" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -30672,7 +30722,7 @@
       </c>
       <c r="AM154" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN154" t="b">
@@ -31232,6 +31282,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA157" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO157" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -31617,7 +31672,7 @@
       </c>
       <c r="AM159" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN159" t="b">
@@ -32177,6 +32232,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA162" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO162" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -32562,7 +32622,7 @@
       </c>
       <c r="AM164" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN164" t="b">
@@ -33512,6 +33572,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA169" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO169" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -34136,7 +34201,7 @@
       </c>
       <c r="AM172" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN172" t="b">
@@ -34696,6 +34761,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA175" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO175" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -35081,7 +35151,7 @@
       </c>
       <c r="AM177" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN177" t="b">
@@ -35641,6 +35711,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA180" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO180" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -36026,7 +36101,7 @@
       </c>
       <c r="AM182" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN182" t="b">
@@ -36586,6 +36661,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA185" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO185" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -36971,7 +37051,7 @@
       </c>
       <c r="AM187" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN187" t="b">
@@ -37531,6 +37611,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA190" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO190" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -37916,7 +38001,7 @@
       </c>
       <c r="AM192" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN192" t="b">
@@ -38476,6 +38561,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA195" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO195" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -38861,7 +38951,7 @@
       </c>
       <c r="AM197" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN197" t="b">
@@ -39421,6 +39511,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA200" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO200" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -39806,7 +39901,7 @@
       </c>
       <c r="AM202" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN202" t="b">
@@ -40366,6 +40461,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA205" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO205" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -40751,7 +40851,7 @@
       </c>
       <c r="AM207" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN207" t="b">
@@ -41311,6 +41411,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA210" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO210" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -41696,7 +41801,7 @@
       </c>
       <c r="AM212" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN212" t="b">
@@ -42256,6 +42361,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA215" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO215" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -42641,7 +42751,7 @@
       </c>
       <c r="AM217" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN217" t="b">
@@ -43201,6 +43311,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA220" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO220" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -43586,7 +43701,7 @@
       </c>
       <c r="AM222" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN222" t="b">
@@ -44146,6 +44261,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA225" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO225" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -44531,7 +44651,7 @@
       </c>
       <c r="AM227" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN227" t="b">
@@ -45481,6 +45601,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA232" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO232" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -46105,7 +46230,7 @@
       </c>
       <c r="AM235" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN235" t="b">
@@ -46665,6 +46790,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA238" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO238" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -47050,7 +47180,7 @@
       </c>
       <c r="AM240" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN240" t="b">
@@ -47610,6 +47740,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA243" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO243" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -47995,7 +48130,7 @@
       </c>
       <c r="AM245" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN245" t="b">
@@ -48555,6 +48690,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA248" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO248" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -48940,7 +49080,7 @@
       </c>
       <c r="AM250" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN250" t="b">
@@ -49500,6 +49640,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA253" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO253" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -49885,7 +50030,7 @@
       </c>
       <c r="AM255" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN255" t="b">
@@ -50445,6 +50590,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA258" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO258" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -50830,7 +50980,7 @@
       </c>
       <c r="AM260" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN260" t="b">
@@ -51390,6 +51540,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA263" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO263" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -51775,7 +51930,7 @@
       </c>
       <c r="AM265" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN265" t="b">
@@ -52335,6 +52490,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA268" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO268" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -52720,7 +52880,7 @@
       </c>
       <c r="AM270" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN270" t="b">
@@ -53280,6 +53440,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA273" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO273" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -53665,7 +53830,7 @@
       </c>
       <c r="AM275" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN275" t="b">
@@ -54225,6 +54390,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA278" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO278" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -54610,7 +54780,7 @@
       </c>
       <c r="AM280" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN280" t="b">
@@ -55170,6 +55340,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA283" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO283" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -55555,7 +55730,7 @@
       </c>
       <c r="AM285" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN285" t="b">
@@ -56115,6 +56290,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA288" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO288" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -56500,7 +56680,7 @@
       </c>
       <c r="AM290" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN290" t="b">

--- a/diseases/d105/1995-1999.xlsx
+++ b/diseases/d105/1995-1999.xlsx
@@ -21538,6 +21538,11 @@
       <c r="Q106" t="n">
         <v>0</v>
       </c>
+      <c r="S106" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA106" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -21550,13 +21555,23 @@
       </c>
       <c r="AP106" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR106" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS106" t="inlineStr"/>
       <c r="AT106" t="n">
         <v>0</v>
       </c>
+      <c r="AU106" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV106" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -22712,6 +22727,11 @@
       <c r="Q112" t="n">
         <v>0</v>
       </c>
+      <c r="S112" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA112" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -22724,13 +22744,23 @@
       </c>
       <c r="AP112" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR112" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS112" t="inlineStr"/>
       <c r="AT112" t="n">
         <v>0</v>
       </c>
+      <c r="AU112" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV112" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -23647,6 +23677,11 @@
       <c r="Q117" t="n">
         <v>0</v>
       </c>
+      <c r="S117" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA117" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -23659,13 +23694,23 @@
       </c>
       <c r="AP117" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR117" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS117" t="inlineStr"/>
       <c r="AT117" t="n">
         <v>0</v>
       </c>
+      <c r="AU117" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV117" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -24582,6 +24627,11 @@
       <c r="Q122" t="n">
         <v>0</v>
       </c>
+      <c r="S122" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA122" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -24594,13 +24644,23 @@
       </c>
       <c r="AP122" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR122" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS122" t="inlineStr"/>
       <c r="AT122" t="n">
         <v>0</v>
       </c>
+      <c r="AU122" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV122" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -25517,6 +25577,11 @@
       <c r="Q127" t="n">
         <v>0</v>
       </c>
+      <c r="S127" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA127" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -25529,13 +25594,23 @@
       </c>
       <c r="AP127" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR127" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS127" t="inlineStr"/>
       <c r="AT127" t="n">
         <v>0</v>
       </c>
+      <c r="AU127" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV127" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -26452,6 +26527,11 @@
       <c r="Q132" t="n">
         <v>0</v>
       </c>
+      <c r="S132" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA132" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -26464,13 +26544,23 @@
       </c>
       <c r="AP132" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR132" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS132" t="inlineStr"/>
       <c r="AT132" t="n">
         <v>0</v>
       </c>
+      <c r="AU132" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV132" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -27387,6 +27477,11 @@
       <c r="Q137" t="n">
         <v>0</v>
       </c>
+      <c r="S137" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA137" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -27399,13 +27494,23 @@
       </c>
       <c r="AP137" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR137" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS137" t="inlineStr"/>
       <c r="AT137" t="n">
         <v>0</v>
       </c>
+      <c r="AU137" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV137" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -28322,6 +28427,11 @@
       <c r="Q142" t="n">
         <v>0</v>
       </c>
+      <c r="S142" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA142" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -28334,13 +28444,23 @@
       </c>
       <c r="AP142" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR142" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS142" t="inlineStr"/>
       <c r="AT142" t="n">
         <v>0</v>
       </c>
+      <c r="AU142" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV142" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -29257,6 +29377,11 @@
       <c r="Q147" t="n">
         <v>0</v>
       </c>
+      <c r="S147" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA147" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -29269,13 +29394,23 @@
       </c>
       <c r="AP147" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR147" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS147" t="inlineStr"/>
       <c r="AT147" t="n">
         <v>0</v>
       </c>
+      <c r="AU147" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV147" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -30192,6 +30327,11 @@
       <c r="Q152" t="n">
         <v>0</v>
       </c>
+      <c r="S152" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA152" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -30204,13 +30344,23 @@
       </c>
       <c r="AP152" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR152" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS152" t="inlineStr"/>
       <c r="AT152" t="n">
         <v>0</v>
       </c>
+      <c r="AU152" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV152" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -31127,6 +31277,11 @@
       <c r="Q157" t="n">
         <v>0</v>
       </c>
+      <c r="S157" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA157" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -31139,13 +31294,23 @@
       </c>
       <c r="AP157" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR157" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS157" t="inlineStr"/>
       <c r="AT157" t="n">
         <v>0</v>
       </c>
+      <c r="AU157" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV157" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -32062,6 +32227,11 @@
       <c r="Q162" t="n">
         <v>0</v>
       </c>
+      <c r="S162" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA162" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -32074,13 +32244,23 @@
       </c>
       <c r="AP162" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR162" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS162" t="inlineStr"/>
       <c r="AT162" t="n">
         <v>0</v>
       </c>
+      <c r="AU162" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV162" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -33387,6 +33567,11 @@
       <c r="Q169" t="n">
         <v>0</v>
       </c>
+      <c r="S169" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA169" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -33399,13 +33584,23 @@
       </c>
       <c r="AP169" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR169" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS169" t="inlineStr"/>
       <c r="AT169" t="n">
         <v>0</v>
       </c>
+      <c r="AU169" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV169" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -34561,6 +34756,11 @@
       <c r="Q175" t="n">
         <v>0</v>
       </c>
+      <c r="S175" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA175" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -34573,13 +34773,23 @@
       </c>
       <c r="AP175" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR175" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS175" t="inlineStr"/>
       <c r="AT175" t="n">
         <v>0</v>
       </c>
+      <c r="AU175" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV175" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -35496,6 +35706,11 @@
       <c r="Q180" t="n">
         <v>0</v>
       </c>
+      <c r="S180" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA180" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -35508,13 +35723,23 @@
       </c>
       <c r="AP180" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR180" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS180" t="inlineStr"/>
       <c r="AT180" t="n">
         <v>0</v>
       </c>
+      <c r="AU180" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV180" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -36431,6 +36656,11 @@
       <c r="Q185" t="n">
         <v>0</v>
       </c>
+      <c r="S185" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA185" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -36443,13 +36673,23 @@
       </c>
       <c r="AP185" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR185" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS185" t="inlineStr"/>
       <c r="AT185" t="n">
         <v>0</v>
       </c>
+      <c r="AU185" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV185" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -37366,6 +37606,11 @@
       <c r="Q190" t="n">
         <v>0</v>
       </c>
+      <c r="S190" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA190" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -37378,13 +37623,23 @@
       </c>
       <c r="AP190" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR190" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS190" t="inlineStr"/>
       <c r="AT190" t="n">
         <v>0</v>
       </c>
+      <c r="AU190" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV190" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -38301,6 +38556,11 @@
       <c r="Q195" t="n">
         <v>0</v>
       </c>
+      <c r="S195" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA195" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -38313,13 +38573,23 @@
       </c>
       <c r="AP195" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR195" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS195" t="inlineStr"/>
       <c r="AT195" t="n">
         <v>0</v>
       </c>
+      <c r="AU195" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV195" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -39236,6 +39506,11 @@
       <c r="Q200" t="n">
         <v>0</v>
       </c>
+      <c r="S200" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA200" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -39248,13 +39523,23 @@
       </c>
       <c r="AP200" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR200" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS200" t="inlineStr"/>
       <c r="AT200" t="n">
         <v>0</v>
       </c>
+      <c r="AU200" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV200" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -40171,6 +40456,11 @@
       <c r="Q205" t="n">
         <v>0</v>
       </c>
+      <c r="S205" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA205" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -40183,13 +40473,23 @@
       </c>
       <c r="AP205" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR205" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS205" t="inlineStr"/>
       <c r="AT205" t="n">
         <v>0</v>
       </c>
+      <c r="AU205" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV205" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -41106,6 +41406,11 @@
       <c r="Q210" t="n">
         <v>0</v>
       </c>
+      <c r="S210" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA210" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -41118,13 +41423,23 @@
       </c>
       <c r="AP210" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR210" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS210" t="inlineStr"/>
       <c r="AT210" t="n">
         <v>0</v>
       </c>
+      <c r="AU210" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV210" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -42041,6 +42356,11 @@
       <c r="Q215" t="n">
         <v>0</v>
       </c>
+      <c r="S215" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA215" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -42053,13 +42373,23 @@
       </c>
       <c r="AP215" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR215" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS215" t="inlineStr"/>
       <c r="AT215" t="n">
         <v>0</v>
       </c>
+      <c r="AU215" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV215" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -42976,6 +43306,11 @@
       <c r="Q220" t="n">
         <v>0</v>
       </c>
+      <c r="S220" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA220" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -42988,13 +43323,23 @@
       </c>
       <c r="AP220" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR220" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS220" t="inlineStr"/>
       <c r="AT220" t="n">
         <v>0</v>
       </c>
+      <c r="AU220" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV220" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -43911,6 +44256,11 @@
       <c r="Q225" t="n">
         <v>0</v>
       </c>
+      <c r="S225" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA225" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -43923,13 +44273,23 @@
       </c>
       <c r="AP225" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR225" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS225" t="inlineStr"/>
       <c r="AT225" t="n">
         <v>0</v>
       </c>
+      <c r="AU225" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV225" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -45236,6 +45596,11 @@
       <c r="Q232" t="n">
         <v>0</v>
       </c>
+      <c r="S232" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA232" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -45248,13 +45613,23 @@
       </c>
       <c r="AP232" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR232" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS232" t="inlineStr"/>
       <c r="AT232" t="n">
         <v>0</v>
       </c>
+      <c r="AU232" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV232" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -46410,6 +46785,11 @@
       <c r="Q238" t="n">
         <v>0</v>
       </c>
+      <c r="S238" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA238" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -46422,13 +46802,23 @@
       </c>
       <c r="AP238" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR238" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS238" t="inlineStr"/>
       <c r="AT238" t="n">
         <v>0</v>
       </c>
+      <c r="AU238" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV238" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -47345,6 +47735,11 @@
       <c r="Q243" t="n">
         <v>0</v>
       </c>
+      <c r="S243" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA243" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -47357,13 +47752,23 @@
       </c>
       <c r="AP243" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR243" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS243" t="inlineStr"/>
       <c r="AT243" t="n">
         <v>0</v>
       </c>
+      <c r="AU243" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV243" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -48280,6 +48685,11 @@
       <c r="Q248" t="n">
         <v>0</v>
       </c>
+      <c r="S248" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA248" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -48292,13 +48702,23 @@
       </c>
       <c r="AP248" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR248" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS248" t="inlineStr"/>
       <c r="AT248" t="n">
         <v>0</v>
       </c>
+      <c r="AU248" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV248" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -49215,6 +49635,11 @@
       <c r="Q253" t="n">
         <v>0</v>
       </c>
+      <c r="S253" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA253" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -49227,13 +49652,23 @@
       </c>
       <c r="AP253" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR253" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS253" t="inlineStr"/>
       <c r="AT253" t="n">
         <v>0</v>
       </c>
+      <c r="AU253" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV253" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -50150,6 +50585,11 @@
       <c r="Q258" t="n">
         <v>0</v>
       </c>
+      <c r="S258" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA258" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -50162,13 +50602,23 @@
       </c>
       <c r="AP258" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR258" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS258" t="inlineStr"/>
       <c r="AT258" t="n">
         <v>0</v>
       </c>
+      <c r="AU258" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV258" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -51085,6 +51535,11 @@
       <c r="Q263" t="n">
         <v>0</v>
       </c>
+      <c r="S263" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA263" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -51097,13 +51552,23 @@
       </c>
       <c r="AP263" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR263" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS263" t="inlineStr"/>
       <c r="AT263" t="n">
         <v>0</v>
       </c>
+      <c r="AU263" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV263" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -52020,6 +52485,11 @@
       <c r="Q268" t="n">
         <v>0</v>
       </c>
+      <c r="S268" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA268" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -52032,13 +52502,23 @@
       </c>
       <c r="AP268" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR268" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS268" t="inlineStr"/>
       <c r="AT268" t="n">
         <v>0</v>
       </c>
+      <c r="AU268" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV268" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -52955,6 +53435,11 @@
       <c r="Q273" t="n">
         <v>0</v>
       </c>
+      <c r="S273" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA273" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -52967,13 +53452,23 @@
       </c>
       <c r="AP273" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR273" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS273" t="inlineStr"/>
       <c r="AT273" t="n">
         <v>0</v>
       </c>
+      <c r="AU273" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV273" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -53890,6 +54385,11 @@
       <c r="Q278" t="n">
         <v>0</v>
       </c>
+      <c r="S278" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA278" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -53902,13 +54402,23 @@
       </c>
       <c r="AP278" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR278" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS278" t="inlineStr"/>
       <c r="AT278" t="n">
         <v>0</v>
       </c>
+      <c r="AU278" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV278" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -54825,6 +55335,11 @@
       <c r="Q283" t="n">
         <v>0</v>
       </c>
+      <c r="S283" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA283" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -54837,13 +55352,23 @@
       </c>
       <c r="AP283" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR283" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS283" t="inlineStr"/>
       <c r="AT283" t="n">
         <v>0</v>
       </c>
+      <c r="AU283" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV283" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -55760,6 +56285,11 @@
       <c r="Q288" t="n">
         <v>0</v>
       </c>
+      <c r="S288" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA288" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -55772,12 +56302,22 @@
       </c>
       <c r="AP288" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR288" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS288" t="inlineStr"/>
       <c r="AT288" t="n">
         <v>0</v>
+      </c>
+      <c r="AU288" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV288" t="inlineStr">
         <is>
